--- a/Testes/reescala/Teste populacao e gerações/Teste1/1_populacao_final.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste1/1_populacao_final.xlsx
@@ -3639,8 +3639,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -4023,8 +4023,8 @@
       <c r="AC30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="4" t="n">
-        <v>1</v>
+      <c r="AD30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
         <v>0</v>
@@ -4123,8 +4123,8 @@
       <c r="X31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
         <v>0</v>
@@ -4674,8 +4674,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -10000,8 +10000,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -11035,8 +11035,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -16361,8 +16361,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -16388,8 +16388,8 @@
       <c r="Y27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="5" t="n">
-        <v>0</v>
+      <c r="Z27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="5" t="n">
         <v>0</v>
@@ -16745,8 +16745,8 @@
       <c r="AC30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="4" t="n">
-        <v>1</v>
+      <c r="AD30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
         <v>0</v>
@@ -16845,8 +16845,8 @@
       <c r="X31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
         <v>0</v>
@@ -17396,8 +17396,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -21396,8 +21396,8 @@
       <c r="AH15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" s="4" t="n">
-        <v>1</v>
+      <c r="AI15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AJ15" s="6">
         <f>SUM(F15:AI15)</f>
@@ -22722,8 +22722,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -22749,8 +22749,8 @@
       <c r="Y27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="5" t="n">
-        <v>0</v>
+      <c r="Z27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="5" t="n">
         <v>0</v>
@@ -23106,8 +23106,8 @@
       <c r="AC30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="4" t="n">
-        <v>1</v>
+      <c r="AD30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
         <v>0</v>
@@ -23206,8 +23206,8 @@
       <c r="X31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
         <v>0</v>
@@ -23757,8 +23757,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -25147,7 +25147,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -29083,8 +29083,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -29467,8 +29467,8 @@
       <c r="AC30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="4" t="n">
-        <v>1</v>
+      <c r="AD30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
         <v>0</v>
@@ -29567,8 +29567,8 @@
       <c r="X31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
         <v>0</v>
@@ -30118,8 +30118,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -31508,7 +31508,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -31894,8 +31894,8 @@
       <c r="AG51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH51" s="4" t="n">
-        <v>1</v>
+      <c r="AH51" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI51" s="5" t="n">
         <v>0</v>
@@ -35444,8 +35444,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -35828,8 +35828,8 @@
       <c r="AC30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="4" t="n">
-        <v>1</v>
+      <c r="AD30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
         <v>0</v>
@@ -35928,8 +35928,8 @@
       <c r="X31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
         <v>0</v>
@@ -36406,8 +36406,8 @@
       <c r="AD35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE35" s="4" t="n">
-        <v>1</v>
+      <c r="AE35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AF35" s="5" t="n">
         <v>0</v>
@@ -36479,8 +36479,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -37869,7 +37869,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -41805,8 +41805,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -42189,8 +42189,8 @@
       <c r="AC30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="4" t="n">
-        <v>1</v>
+      <c r="AD30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
         <v>0</v>
@@ -42289,8 +42289,8 @@
       <c r="X31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
         <v>0</v>
@@ -42840,8 +42840,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -48166,8 +48166,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -48193,8 +48193,8 @@
       <c r="Y27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="5" t="n">
-        <v>0</v>
+      <c r="Z27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="5" t="n">
         <v>0</v>
@@ -49201,8 +49201,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -50591,7 +50591,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -54527,8 +54527,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -55562,8 +55562,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -60434,8 +60434,8 @@
       <c r="R23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="5" t="n">
-        <v>0</v>
+      <c r="S23" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="T23" s="5" t="n">
         <v>0</v>
@@ -60888,8 +60888,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -60915,8 +60915,8 @@
       <c r="Y27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="5" t="n">
-        <v>0</v>
+      <c r="Z27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="5" t="n">
         <v>0</v>
@@ -61923,8 +61923,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -63313,7 +63313,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
